--- a/excel_import_template_extended.xlsx
+++ b/excel_import_template_extended.xlsx
@@ -424,20 +424,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K27"/>
+  <dimension ref="A1:L28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="42" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="56" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="56" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -463,35 +464,40 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>分值</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>题干</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>选项A</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>选项B</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>选项C</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>选项D</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>正确答案</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
@@ -516,37 +522,40 @@
       <c r="D2" t="n">
         <v>1</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2" t="inlineStr">
         <is>
           <t>函数 y=x^3 在 x=1 处的导数是多少？</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>y'=3x^2，代入 x=1 得 3。</t>
         </is>
@@ -571,37 +580,38 @@
       <c r="D3" t="n">
         <v>2</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
         <is>
           <t>半径为 3 的圆面积是多少？</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>6pi</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>9pi</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>12pi</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>18pi</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>圆面积公式为 S=pi r^2。</t>
         </is>
@@ -626,37 +636,40 @@
       <c r="D4" t="n">
         <v>3</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>方程 x^2-5x+6=0 的解是？</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>1 和 6</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>2 和 3</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>3 和 5</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>1 和 5</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>因式分解为 (x-2)(x-3)=0。</t>
         </is>
@@ -681,21 +694,22 @@
       <c r="D5" t="n">
         <v>1</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
         <is>
           <t>请填写成语：专心____。</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
         <is>
           <t>致志</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>常见成语为专心致志。</t>
         </is>
@@ -720,21 +734,24 @@
       <c r="D6" t="n">
         <v>2</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>补全诗句：海内存知己，天涯若比____。</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
         <is>
           <t>邻</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>完整诗句为天涯若比邻。</t>
         </is>
@@ -759,21 +776,22 @@
       <c r="D7" t="n">
         <v>2</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
         <is>
           <t>“通过这次学习，使我提高了成绩。”这句话没有语病。</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>该句缺少主语，属于病句。</t>
         </is>
@@ -798,37 +816,40 @@
       <c r="D8" t="n">
         <v>1</v>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" t="inlineStr">
         <is>
           <t>She ____ to school every day.</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>go</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>goes</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>going</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>gone</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>主语为第三人称单数，动词用 goes。</t>
         </is>
@@ -853,21 +874,22 @@
       <c r="D9" t="n">
         <v>2</v>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
         <is>
           <t>Please ____ the door when you leave.</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
         <is>
           <t>close</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>句意为离开时请关门。</t>
         </is>
@@ -892,37 +914,40 @@
       <c r="D10" t="n">
         <v>2</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" t="n">
+        <v>5</v>
+      </c>
+      <c r="F10" t="inlineStr">
         <is>
           <t>以下哪些词可以作介词？</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>in</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>quickly</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>A,B,D</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>in、on、under 都可作介词，quickly 是副词。</t>
         </is>
@@ -947,21 +972,22 @@
       <c r="D11" t="n">
         <v>1</v>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
         <is>
           <t>English has 26 letters.</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>英语字母表共有 26 个字母。</t>
         </is>
@@ -986,37 +1012,38 @@
       <c r="D12" t="n">
         <v>1</v>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
         <is>
           <t>Python 中用于定义函数的关键字是？</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>func</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>def</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>function</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>lambda</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>标准函数定义关键字为 def。</t>
         </is>
@@ -1041,37 +1068,40 @@
       <c r="D13" t="n">
         <v>2</v>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" t="n">
+        <v>4</v>
+      </c>
+      <c r="F13" t="inlineStr">
         <is>
           <t>以下哪些属于 Python 容器类型？</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>list</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>dict</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>set</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>print</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>A,B,C</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>list、dict、set 都是容器，print 是函数。</t>
         </is>
@@ -1096,37 +1126,38 @@
       <c r="D14" t="n">
         <v>2</v>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
         <is>
           <t>用于网页传输的常见协议是？</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>FTP</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>SMTP</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>HTTP</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>SSH</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>网页浏览最常见的是 HTTP/HTTPS。</t>
         </is>
@@ -1151,21 +1182,24 @@
       <c r="D15" t="n">
         <v>3</v>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E15" t="n">
+        <v>2</v>
+      </c>
+      <c r="F15" t="inlineStr">
         <is>
           <t>强密码通常应包含大小写字母、数字和符号。</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>这是密码安全的基本建议。</t>
         </is>
@@ -1190,21 +1224,22 @@
       <c r="D16" t="n">
         <v>1</v>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
         <is>
           <t>水在标准大气压下 100 摄氏度沸腾。</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>这是基础物理常识。</t>
         </is>
@@ -1229,37 +1264,40 @@
       <c r="D17" t="n">
         <v>1</v>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E17" t="n">
+        <v>2</v>
+      </c>
+      <c r="F17" t="inlineStr">
         <is>
           <t>中国的首都是哪座城市？</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>上海</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>北京</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>广州</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>深圳</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>中国首都是北京。</t>
         </is>
@@ -1284,37 +1322,38 @@
       <c r="D18" t="n">
         <v>3</v>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
         <is>
           <t>以下哪些属于中国古代四大发明？</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>造纸术</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>火药</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>指南针</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>显微镜</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>A,B,C</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>显微镜不属于四大发明。</t>
         </is>
@@ -1339,37 +1378,40 @@
       <c r="D19" t="n">
         <v>2</v>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E19" t="n">
+        <v>3</v>
+      </c>
+      <c r="F19" t="inlineStr">
         <is>
           <t>力的国际单位是？</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>牛顿</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>焦耳</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>瓦特</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>帕斯卡</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>力的单位是牛顿。</t>
         </is>
@@ -1394,21 +1436,22 @@
       <c r="D20" t="n">
         <v>1</v>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
         <is>
           <t>请填写元素符号：氧是 ____。</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr">
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t>氧元素符号为 O。</t>
         </is>
@@ -1433,37 +1476,40 @@
       <c r="D21" t="n">
         <v>2</v>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E21" t="n">
+        <v>3</v>
+      </c>
+      <c r="F21" t="inlineStr">
         <is>
           <t>人体中负责输送血液的器官是？</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>肺</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>胃</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>心脏</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>肝脏</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>心脏负责泵送血液。</t>
         </is>
@@ -1498,12 +1544,19 @@
     <row r="26">
       <c r="B26" t="inlineStr">
         <is>
-          <t>多选题答案用英文逗号分隔，例如 A,B,D。</t>
+          <t>分值列可手工填写；留空时会使用题型默认分值。</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="B27" t="inlineStr">
+        <is>
+          <t>多选题答案用英文逗号分隔，例如 A,B,D。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="inlineStr">
         <is>
           <t>本模板共 20 道题，可直接导入后再批量修改为你的题库内容。</t>
         </is>
